--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/16</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -842,22 +842,22 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1001,12 +1001,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1056,1454 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,17 +689,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -713,17 +709,13 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -862,32 +854,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -895,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,33 +915,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1228,7 +1232,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1252,33 +1256,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1389,7 +1397,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1417,32 +1425,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1450,7 +1462,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1474,33 +1486,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1611,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1722,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1833,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1944,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2055,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2166,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2277,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2388,7 +2404,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2422,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2449,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2463,7 +2479,7 @@
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2493,17 +2509,802 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>1/16</t>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3197,22 +3197,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3294,17 +3294,239 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="AC25" s="2" t="inlineStr">
+      <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +819,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -930,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -945,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1117,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1232,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1351,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1386,7 +1390,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1462,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1516,7 +1520,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1581,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1616,7 +1620,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1655,32 +1659,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1688,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,17 +1720,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1732,13 +1740,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1766,32 +1778,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1799,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1823,33 +1839,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1897,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1910,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,33 +1958,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1988,32 +2016,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2021,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2045,33 +2077,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2168,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2210,32 +2246,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2243,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,33 +2307,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2321,32 +2365,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2354,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2378,33 +2426,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2484,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2465,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2489,17 +2545,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2509,13 +2565,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2636,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2747,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2726,7 +2786,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2741,7 +2801,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2862,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2841,7 +2901,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2913,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3024,7 +3084,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,7 +3138,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3199,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3310,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3361,7 +3421,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3415,7 +3475,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3536,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3520,13 +3580,1040 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr"/>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,13 +1165,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1275,22 +1279,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1390,7 +1394,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1466,7 +1470,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1505,17 +1509,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1581,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1696,7 +1700,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1735,22 +1739,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1819,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1854,7 +1858,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1869,7 +1873,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2337,7 +2341,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2406,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2521,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2575,7 +2579,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2607,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2636,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2660,17 +2668,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2680,13 +2688,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +2985,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3012,7 +3024,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3051,32 +3063,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3084,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3108,37 +3124,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3277,32 +3293,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -3310,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3334,17 +3354,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3354,13 +3374,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3388,32 +3412,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3421,7 +3449,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3445,32 +3473,32 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3503,32 +3531,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3536,7 +3568,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3560,37 +3592,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3683,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3690,7 +3722,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3762,7 +3794,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,7 +3905,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3912,7 +3944,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3927,7 +3959,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3988,7 +4020,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4042,7 +4074,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4135,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4157,7 +4189,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4250,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4272,7 +4304,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4365,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4448,7 +4480,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4559,7 +4591,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4617,6 +4649,688 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,18 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1175,7 +1179,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1298,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1470,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1509,7 +1513,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1524,7 +1528,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1754,7 +1758,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1873,7 +1877,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1977,22 +1981,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2096,22 +2100,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2326,17 +2330,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2406,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2460,7 +2464,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2583,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2702,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2798,22 +2802,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2913,18 +2917,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3024,7 +3032,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3100,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3154,7 +3162,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3392,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3488,7 +3496,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3503,7 +3511,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3622,7 +3630,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3905,7 +3913,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3959,7 +3967,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3987,32 +3995,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4020,7 +4032,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4044,37 +4056,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4102,32 +4114,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4135,7 +4151,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4159,37 +4175,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4217,32 +4233,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4250,7 +4270,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4274,32 +4294,32 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4365,7 +4385,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4419,7 +4439,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4447,32 +4467,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4480,7 +4504,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4504,33 +4528,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4558,32 +4586,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4591,7 +4623,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4615,37 +4647,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4738,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4760,7 +4792,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4853,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4860,7 +4892,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4932,7 +4964,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4971,7 +5003,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4986,7 +5018,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5079,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5101,7 +5133,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5194,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5220,22 +5252,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5273,7 +5305,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5287,47 +5319,848 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>111.0</t>
         </is>
       </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>12/18</t>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1058,13 +1058,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1398,18 +1402,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1518,17 +1526,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1766,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1862,22 +1870,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1981,22 +1989,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2100,22 +2108,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2330,7 +2338,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2345,7 +2353,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2472,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2812,12 +2820,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2932,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2993,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3037,13 +3045,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3501,17 +3513,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3642,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3730,18 +3742,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3952,22 +3968,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4071,22 +4087,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4190,22 +4206,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4309,7 +4325,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4324,7 +4340,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4558,7 +4574,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4612,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4623,7 +4639,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4672,12 +4688,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4808,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4820,32 +4836,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4853,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4877,17 +4897,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4897,13 +4917,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4931,32 +4955,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4964,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4988,17 +5016,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5008,17 +5036,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5161,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5161,32 +5189,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5194,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5218,33 +5250,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5272,32 +5308,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5305,7 +5345,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5329,37 +5369,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5387,32 +5427,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5420,7 +5464,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5444,37 +5488,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5579,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5574,7 +5618,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5589,7 +5633,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5617,32 +5661,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5650,7 +5698,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5674,37 +5722,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5813,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5819,7 +5867,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5928,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5929,12 +5977,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5995,7 +6043,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6039,13 +6087,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6158,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6150,17 +6202,592 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>7/18</t>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4330,17 +4330,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4678,22 +4678,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4912,22 +4912,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5437,24 +5437,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5546,32 +5546,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5579,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5603,17 +5607,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5623,17 +5627,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5671,24 +5675,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5698,7 +5702,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5747,12 +5751,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5780,32 +5784,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5813,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5837,27 +5845,27 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5895,32 +5903,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5928,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5952,37 +5964,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6010,32 +6022,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6043,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6067,37 +6083,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6125,32 +6141,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6158,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6182,27 +6202,27 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6273,7 +6293,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6327,7 +6347,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6408,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6442,7 +6462,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6523,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6552,7 +6572,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6618,7 +6638,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6662,17 +6682,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6753,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6782,12 +6802,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,17 +1402,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3742,17 +3742,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3973,17 +3973,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4087,17 +4087,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5265,17 +5265,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5384,17 +5384,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,17 +5508,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5913,24 +5913,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5989,12 +5989,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6032,24 +6032,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6151,24 +6151,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6260,32 +6260,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6293,7 +6297,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6317,32 +6321,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6375,32 +6379,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6408,7 +6416,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6432,32 +6440,32 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6490,32 +6498,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6523,7 +6535,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6547,17 +6559,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6567,17 +6579,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6650,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6692,7 +6704,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6765,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,7 +6880,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,7 +6995,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7032,12 +7044,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7110,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7147,7 +7159,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7213,7 +7225,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7262,7 +7274,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7328,7 +7340,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7382,7 +7394,348 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4330,17 +4330,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5627,17 +5627,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5746,17 +5746,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6508,12 +6508,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6617,32 +6617,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6650,7 +6654,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6674,17 +6678,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6694,17 +6698,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6732,32 +6736,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6765,7 +6773,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6789,17 +6797,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6809,17 +6817,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6888,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,7 +7003,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,7 +7118,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,7 +7233,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7348,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,7 +7463,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7570,7 +7578,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7624,7 +7632,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7632,22 +7640,22 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7680,12 +7688,12 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7699,41 +7707,271 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr"/>
-      <c r="AC62" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1058,17 +1058,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,17 +1526,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1989,22 +1989,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2338,22 +2338,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>89.0</t>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,17 +3045,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,17 +3513,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4206,22 +4206,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4325,22 +4325,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4678,22 +4678,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq21推进至seq34，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4762,10 +4762,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4793,7 +4805,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4808,7 +4820,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4917,17 +4929,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5004,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5036,17 +5048,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5119,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5161,7 +5173,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5280,7 +5292,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5357,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5399,7 +5411,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5476,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5518,7 +5530,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5622,22 +5634,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5741,22 +5753,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5833,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5860,12 +5872,12 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5875,7 +5887,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5979,22 +5991,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6103,17 +6115,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6190,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6222,17 +6234,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6351,7 +6363,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6428,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6470,7 +6482,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6547,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6589,7 +6601,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -6627,24 +6639,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6654,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6693,22 +6705,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6758,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6773,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6812,22 +6824,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6867,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6888,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6912,27 +6928,27 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6942,7 +6958,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6970,32 +6986,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7003,7 +7023,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7027,37 +7047,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -7085,32 +7105,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7118,7 +7142,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7142,17 +7166,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7162,17 +7186,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -7200,32 +7224,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7233,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7257,17 +7285,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7277,17 +7305,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7376,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7402,7 +7430,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7491,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7517,7 +7545,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7606,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7632,7 +7660,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7721,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7747,7 +7775,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7836,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7862,7 +7890,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7951,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7973,7 +8001,923 @@
       <c r="AB64" s="2" t="inlineStr"/>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>12/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1168,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,22 +1402,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,22 +1521,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,22 +2108,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,18 +2223,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2338,22 +2342,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2472,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,22 +2580,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2710,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2825,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2940,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3040,7 +3044,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3120,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3174,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3389,22 +3393,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3508,22 +3512,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,7 +3631,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3642,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3742,22 +3746,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3968,22 +3972,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4087,22 +4091,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4221,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4325,22 +4329,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4455,7 +4459,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4574,7 +4578,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4693,7 +4697,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4820,7 +4824,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4924,7 +4928,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5004,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5043,22 +5047,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5086,12 +5090,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程39%处后消失；随后反向物理轨迹由seq23推进至seq37，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5119,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5127,10 +5131,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq17映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5158,7 +5174,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5173,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5277,22 +5293,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5396,22 +5412,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5515,22 +5531,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5634,22 +5650,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5768,7 +5784,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5887,7 +5903,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6006,7 +6022,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6110,7 +6126,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6190,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6229,22 +6245,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6348,22 +6364,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6467,22 +6483,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6586,22 +6602,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6705,22 +6721,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6839,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6958,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7077,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7181,7 +7197,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7234,12 +7250,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7261,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7300,22 +7316,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -7343,32 +7359,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7376,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7400,37 +7420,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -7458,32 +7478,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7491,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7515,37 +7539,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7573,32 +7597,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7606,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7630,37 +7658,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7716,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7721,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7745,37 +7777,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -7803,32 +7835,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7836,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7860,37 +7896,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7954,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7951,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7975,33 +8015,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -8029,32 +8073,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8062,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8086,37 +8134,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8144,32 +8192,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>14:40</t>
@@ -8177,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8201,17 +8253,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8221,13 +8273,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8342,7 +8398,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8457,7 +8513,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8572,7 +8628,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8689,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8687,7 +8743,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8804,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8802,7 +8858,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8919,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8917,7 +8973,1157 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>12/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>2/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>15/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>3/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,22 +1521,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,22 +1751,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1989,22 +1989,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,22 +2461,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2929,22 +2929,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,22 +3163,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,22 +3512,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,22 +3631,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4210,22 +4210,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4444,22 +4444,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4563,22 +4563,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4809,22 +4809,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5047,22 +5047,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5769,22 +5769,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5888,22 +5888,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6245,22 +6245,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7316,22 +7316,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8083,24 +8083,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8268,22 +8268,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -8426,32 +8426,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8459,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8483,37 +8487,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8541,32 +8545,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8574,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8598,37 +8606,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -8656,32 +8664,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8689,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8713,37 +8725,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8771,32 +8783,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8804,7 +8820,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8828,37 +8844,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8958,7 +8974,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -8973,7 +8989,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -9001,32 +9017,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9034,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9058,37 +9078,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9169,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9231,32 +9251,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9264,7 +9288,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9288,37 +9312,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9403,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9433,7 +9457,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9518,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9609,7 +9633,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9724,7 +9748,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9839,7 +9863,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9893,7 +9917,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9978,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10069,7 +10093,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10118,12 +10142,1047 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
           <t>3/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2223,22 +2223,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3972,22 +3972,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4928,17 +4928,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5412,17 +5412,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,22 +5531,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6483,17 +6483,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6602,22 +6602,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7197,17 +7197,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,22 +7435,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,17 +7559,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7673,17 +7673,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7792,22 +7792,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -9136,32 +9136,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9169,7 +9173,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9193,32 +9197,32 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9261,24 +9265,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9288,7 +9292,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9337,12 +9341,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -9370,32 +9374,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9403,7 +9411,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9427,37 +9435,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -9485,32 +9493,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9518,7 +9530,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9542,17 +9554,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9562,17 +9574,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -9600,32 +9612,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9633,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9657,32 +9673,32 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9715,32 +9731,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9748,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9772,37 +9792,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -9830,32 +9850,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9863,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9887,37 +9911,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -9978,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10017,7 +10041,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10032,7 +10056,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -10060,32 +10084,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10093,7 +10121,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10117,17 +10145,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10137,12 +10165,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10208,7 +10236,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10262,7 +10290,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10351,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10362,7 +10390,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10438,7 +10466,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10492,7 +10520,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10581,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10592,7 +10620,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10607,7 +10635,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10696,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10722,7 +10750,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10811,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10837,7 +10865,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10883,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -10898,7 +10926,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10912,7 +10940,7 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
@@ -11013,7 +11041,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11067,7 +11095,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11156,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11177,12 +11205,932 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>1/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,17 +1526,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,22 +1751,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,17 +3517,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,22 +3631,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4444,17 +4444,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5052,17 +5052,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,17 +6250,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,17 +7321,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8268,22 +8268,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8740,17 +8740,17 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9093,22 +9093,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,17 +9336,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -9969,32 +9969,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10002,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,17 +10030,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10046,17 +10050,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -10203,32 +10207,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>14:40</t>
@@ -10236,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10260,37 +10268,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>17/19</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10405,7 +10413,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -10433,32 +10441,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10466,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10490,17 +10502,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10510,12 +10522,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10548,32 +10560,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10581,7 +10597,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10605,17 +10621,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10625,12 +10641,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10663,32 +10679,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10696,7 +10716,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10720,32 +10740,32 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10778,32 +10798,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10811,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10835,17 +10859,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10855,12 +10879,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10893,32 +10917,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10926,7 +10954,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10950,17 +10978,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10970,12 +10998,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11008,32 +11036,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11041,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11065,37 +11097,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -11123,32 +11155,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11156,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11180,17 +11216,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11200,17 +11236,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -11271,7 +11307,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11386,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11440,7 +11476,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11540,7 +11576,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11555,7 +11591,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11652,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11670,7 +11706,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11767,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11785,7 +11821,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>17/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11882,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11900,7 +11936,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11997,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12005,17 +12041,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12112,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12120,17 +12156,477 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>92.2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>90.7</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>14/19</t>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>91.8</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>3/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4096,17 +4096,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,17 +6488,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7440,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7678,17 +7678,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9455,17 +9455,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9693,17 +9693,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11165,12 +11165,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11241,12 +11241,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -11389,32 +11389,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11422,7 +11426,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11446,17 +11450,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11466,17 +11470,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -11504,32 +11508,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11537,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11561,17 +11569,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11581,17 +11589,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11660,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11767,7 +11775,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11882,7 +11890,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11997,7 +12005,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12036,7 +12044,7 @@
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
@@ -12112,7 +12120,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12166,7 +12174,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12235,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12342,7 +12350,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12457,7 +12465,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12572,7 +12580,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12616,17 +12624,132 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB103" s="2" t="inlineStr">
-        <is>
-          <t>88.3</t>
-        </is>
-      </c>
-      <c r="AC103" s="2" t="inlineStr">
-        <is>
-          <t>7/19</t>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>93.7</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>16/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,17 +3168,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3977,17 +3977,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4814,17 +4814,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5536,17 +5536,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8268,17 +8268,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8388,17 +8388,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,17 +8626,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10050,17 +10050,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10283,17 +10283,17 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10403,17 +10403,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,17 +10641,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>9/19</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>16/19</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/19</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -11742,32 +11742,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11775,7 +11779,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11799,17 +11803,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11819,17 +11823,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>15/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -11857,32 +11861,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11890,7 +11898,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11914,17 +11922,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11934,17 +11942,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -11972,32 +11980,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12005,7 +12017,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12029,17 +12041,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12049,17 +12061,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/19</t>
+          <t>11/19</t>
         </is>
       </c>
     </row>
@@ -12087,32 +12099,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12120,7 +12136,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12144,17 +12160,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12164,17 +12180,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -12202,32 +12218,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>14:40</t>
@@ -12235,7 +12255,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12259,32 +12279,32 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12350,7 +12370,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12404,7 +12424,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12485,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12504,7 +12524,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12519,7 +12539,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -12580,7 +12600,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12634,7 +12654,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12715,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12739,17 +12759,247 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB104" s="2" t="inlineStr">
-        <is>
-          <t>93.7</t>
-        </is>
-      </c>
-      <c r="AC104" s="2" t="inlineStr">
-        <is>
-          <t>16/19</t>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东78路.xlsx
+++ b/data/export/2026-10-22-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1756,17 +1756,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4449,17 +4449,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7440,17 +7440,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8745,17 +8745,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9098,17 +9098,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9455,17 +9455,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>15/19</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>7/19</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>4/19</t>
         </is>
       </c>
     </row>
@@ -10597,7 +10597,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10760,17 +10760,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>14/19</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11117,17 +11117,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>6/19</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -11990,12 +11990,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12066,12 +12066,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
@@ -12255,7 +12255,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12337,32 +12337,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12370,7 +12374,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12394,17 +12398,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12414,17 +12418,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -12452,32 +12456,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12485,7 +12493,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12509,17 +12517,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12529,17 +12537,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -12567,32 +12575,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12600,7 +12612,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12624,17 +12636,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12644,17 +12656,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12727,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12764,12 +12776,12 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>12/19</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12842,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12879,7 +12891,7 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
@@ -12945,7 +12957,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12989,17 +13001,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
